--- a/05_Figures/F06_prediction/proteins/T1/d_mcsa/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/T1/d_mcsa/spls/c_data/results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="195">
   <si>
     <t xml:space="preserve">level</t>
   </si>
@@ -140,417 +140,444 @@
     <t xml:space="preserve">CBR1</t>
   </si>
   <si>
+    <t xml:space="preserve">COL18A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KRAS</t>
+  </si>
+  <si>
     <t xml:space="preserve">METTL26</t>
   </si>
   <si>
+    <t xml:space="preserve">PAIP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPIL3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPS4X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S100A6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AHCY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CTBP1</t>
+  </si>
+  <si>
     <t xml:space="preserve">DPYSL2</t>
   </si>
   <si>
-    <t xml:space="preserve">PAIP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPIL3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S100A6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTBP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPS4X</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AHCY</t>
+    <t xml:space="preserve">EIF3L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FUBP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPAT3</t>
   </si>
   <si>
     <t xml:space="preserve">ANK2</t>
   </si>
   <si>
-    <t xml:space="preserve">COL18A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GPAT3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KRAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF3L</t>
+    <t xml:space="preserve">ARHGDIB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GMPPB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAVS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MICU2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MPDU1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OSBPL1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SYNC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COPS8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DYNLL1</t>
   </si>
   <si>
     <t xml:space="preserve">FAM114A2</t>
   </si>
   <si>
+    <t xml:space="preserve">GNA11</t>
+  </si>
+  <si>
     <t xml:space="preserve">HEBP1</t>
   </si>
   <si>
-    <t xml:space="preserve">RPN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARHGDIB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GMPPB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OSBPL1A</t>
+    <t xml:space="preserve">NUDT2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THOP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSTB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H6PD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UCHL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPN2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DDX6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PM20D2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLTC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GYG1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S100A13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRMT10C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRDX4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACTR3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDUFS3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NPEPL1</t>
   </si>
   <si>
     <t xml:space="preserve">RAB24</t>
   </si>
   <si>
-    <t xml:space="preserve">SYNC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COPS8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DDX6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DYNLL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FUBP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GNA11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAVS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NUDT2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">THOP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRMT10C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CANX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAPN2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLTC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSTB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H6PD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MICU2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UCHL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GYG1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S100A13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CARS1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MPDU1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NPEPL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRDX4</t>
-  </si>
-  <si>
     <t xml:space="preserve">ACTR2</t>
   </si>
   <si>
-    <t xml:space="preserve">ACTR3</t>
+    <t xml:space="preserve">AKT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARPC4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MTRES1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUBB6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APIP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLIC6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUL2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DNPEP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FABP4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FARSB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FXR1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GANAB</t>
   </si>
   <si>
     <t xml:space="preserve">HARS1</t>
   </si>
   <si>
-    <t xml:space="preserve">TUBB6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APIP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARPC4</t>
+    <t xml:space="preserve">HSPH1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAN2C1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRP14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRPRB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TWF2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UBAP2L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UCHL3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADHFE1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADPRHL2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AHNAK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALDH7A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANK3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANXA2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AP2M1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP5MC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CNIH4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCTN4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCUN1D1</t>
   </si>
   <si>
     <t xml:space="preserve">DPYSL3</t>
   </si>
   <si>
+    <t xml:space="preserve">DTNA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECHDC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF3M</t>
+  </si>
+  <si>
     <t xml:space="preserve">EPB41L2</t>
   </si>
   <si>
-    <t xml:space="preserve">FAH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FARSB</t>
+    <t xml:space="preserve">FHL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GBE1</t>
   </si>
   <si>
     <t xml:space="preserve">GPHN</t>
   </si>
   <si>
+    <t xml:space="preserve">HIST2H2BE</t>
+  </si>
+  <si>
     <t xml:space="preserve">HLA-C</t>
   </si>
   <si>
-    <t xml:space="preserve">MAN2C1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MTRES1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDUFS3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PM20D2</t>
+    <t xml:space="preserve">HMGB1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HNRNPC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HNRNPH3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPCAL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSPB6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMPA1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMPA2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LDHA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LRRC47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MACROD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEMO1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MPI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRPL49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRPL55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MTM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYH9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYO1C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NHLRC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NME2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NUBPL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OCIAD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OSTC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PFKFB1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PMM2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PMPCB</t>
   </si>
   <si>
     <t xml:space="preserve">PPM1B</t>
   </si>
   <si>
-    <t xml:space="preserve">SRPRB</t>
+    <t xml:space="preserve">PPP1CA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPP2R2A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMC4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMD3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RABGGTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REEP5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPS10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPS3A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S100A10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S100A16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SDHA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEC22B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEC31A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SGCG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SHMT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLC25A3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLC44A2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNTA1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STK38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TFG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THAP4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THY1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIMM21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIMMDC1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TKT</t>
   </si>
   <si>
     <t xml:space="preserve">TLN2</t>
   </si>
   <si>
-    <t xml:space="preserve">TWF2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UCHL3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADPRHL2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AHNAK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALDH7A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANXA2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AP2M1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP5MC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CNIH4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CUL2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCTN4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCUN1D1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DTNA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ECHDC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EEA1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF3M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FABP4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FHL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FXR1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GANAB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GBE1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HMGB1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HNRNPH3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPCAL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSPB6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSPH1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMPA1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMPA2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JPT2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LDHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MACROD1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MEMO1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MGLL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MPI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRPL55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MSN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MYH9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MYO1C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NHLRC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NME2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NUBPL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OCIAD1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OSBPL11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OSTC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PACSIN3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PALMD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PFKFB1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PMM2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PMPCB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPP2R2A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMC4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMD3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PTGR1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RABGGTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REEP5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPS10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPS3A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S100A10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S100A16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SDHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEC22B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEC31A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SHMT1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLC44A2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNTA1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRP14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STK38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">THAP4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">THY1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TIMM21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TIMMDC1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TKT</t>
-  </si>
-  <si>
     <t xml:space="preserve">TMEM38A</t>
   </si>
   <si>
@@ -563,9 +590,6 @@
     <t xml:space="preserve">TUBB2A</t>
   </si>
   <si>
-    <t xml:space="preserve">UBAP2L</t>
-  </si>
-  <si>
     <t xml:space="preserve">UBE2V1</t>
   </si>
   <si>
@@ -573,9 +597,6 @@
   </si>
   <si>
     <t xml:space="preserve">VAT1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VDAC1</t>
   </si>
   <si>
     <t xml:space="preserve">WARS1</t>
@@ -965,16 +986,16 @@
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>1903</v>
+        <v>1898</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.185019907607819</v>
+        <v>-0.172867637882008</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0428571428571429</v>
+        <v>0.025</v>
       </c>
       <c r="J2"/>
       <c r="K2"/>
@@ -998,29 +1019,21 @@
         <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>1903</v>
+        <v>1898</v>
       </c>
       <c r="G3" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.185019907607819</v>
+        <v>-0.172867637882008</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0428571428571429</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.248756218905473</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.383084577114428</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-0.598397749471713</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.612453293152583</v>
-      </c>
+        <v>0.025</v>
+      </c>
+      <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1044,2206 +1057,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-0.659579085703874</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="n">
-        <v>-0.93518358657787</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="n">
-        <v>-1.19630922459219</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-0.233296110395571</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="n">
-        <v>-1.29957687526217</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="n">
-        <v>-0.83957082090637</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="n">
-        <v>-0.753334910746579</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-0.170472786211659</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-0.347066718026214</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-1.38342332433722</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-0.409065763990216</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.526228315357393</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-0.549510287328676</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" t="n">
-        <v>-0.210321866796497</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" t="n">
-        <v>-0.388888802357009</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="n">
-        <v>-0.616900627901036</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" t="n">
-        <v>-0.376981356901494</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" t="n">
-        <v>-1.31811327239341</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" t="n">
-        <v>-0.551524590729148</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" t="n">
-        <v>-0.296849420542577</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" t="n">
-        <v>-0.80596953319163</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0.000113093352066995</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0.141088344627245</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-1.56493557002126</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" t="n">
-        <v>-0.151698449444811</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" t="n">
-        <v>-0.780411124606203</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" t="n">
-        <v>-2.34996096870006</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" t="n">
-        <v>-0.0798411628022093</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>15</v>
-      </c>
-      <c r="B30" t="s">
-        <v>16</v>
-      </c>
-      <c r="C30" t="n">
-        <v>-0.170247464272738</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" t="n">
-        <v>-1.02204682500085</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>15</v>
-      </c>
-      <c r="B32" t="s">
-        <v>16</v>
-      </c>
-      <c r="C32" t="n">
-        <v>0.230854255119713</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C33" t="n">
-        <v>-0.434098540769437</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>15</v>
-      </c>
-      <c r="B34" t="s">
-        <v>16</v>
-      </c>
-      <c r="C34" t="n">
-        <v>-0.101614028111065</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>15</v>
-      </c>
-      <c r="B35" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" t="n">
-        <v>-0.517998083881962</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>15</v>
-      </c>
-      <c r="B36" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36" t="n">
-        <v>0.0671490858892299</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>15</v>
-      </c>
-      <c r="B37" t="s">
-        <v>16</v>
-      </c>
-      <c r="C37" t="n">
-        <v>-0.604426189584003</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>15</v>
-      </c>
-      <c r="B38" t="s">
-        <v>16</v>
-      </c>
-      <c r="C38" t="n">
-        <v>-1.25022280889437</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>15</v>
-      </c>
-      <c r="B39" t="s">
-        <v>16</v>
-      </c>
-      <c r="C39" t="n">
-        <v>-0.0305876712755853</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>15</v>
-      </c>
-      <c r="B40" t="s">
-        <v>16</v>
-      </c>
-      <c r="C40" t="n">
-        <v>-0.818323281211485</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>15</v>
-      </c>
-      <c r="B41" t="s">
-        <v>16</v>
-      </c>
-      <c r="C41" t="n">
-        <v>-0.796599610965328</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s">
-        <v>15</v>
-      </c>
-      <c r="B42" t="s">
-        <v>16</v>
-      </c>
-      <c r="C42" t="n">
-        <v>-0.860321821127958</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s">
-        <v>15</v>
-      </c>
-      <c r="B43" t="s">
-        <v>16</v>
-      </c>
-      <c r="C43" t="n">
-        <v>-0.333945934968475</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s">
-        <v>15</v>
-      </c>
-      <c r="B44" t="s">
-        <v>16</v>
-      </c>
-      <c r="C44" t="n">
-        <v>-0.251454455610574</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s">
-        <v>15</v>
-      </c>
-      <c r="B45" t="s">
-        <v>16</v>
-      </c>
-      <c r="C45" t="n">
-        <v>-0.901204734103955</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46" t="s">
-        <v>16</v>
-      </c>
-      <c r="C46" t="n">
-        <v>-0.436252756624727</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s">
-        <v>15</v>
-      </c>
-      <c r="B47" t="s">
-        <v>16</v>
-      </c>
-      <c r="C47" t="n">
-        <v>-0.0683754518804203</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s">
-        <v>15</v>
-      </c>
-      <c r="B48" t="s">
-        <v>16</v>
-      </c>
-      <c r="C48" t="n">
-        <v>-0.528732176284324</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s">
-        <v>15</v>
-      </c>
-      <c r="B49" t="s">
-        <v>16</v>
-      </c>
-      <c r="C49" t="n">
-        <v>-1.50826102975938</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s">
-        <v>15</v>
-      </c>
-      <c r="B50" t="s">
-        <v>16</v>
-      </c>
-      <c r="C50" t="n">
-        <v>0.310622559818857</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s">
-        <v>15</v>
-      </c>
-      <c r="B51" t="s">
-        <v>16</v>
-      </c>
-      <c r="C51" t="n">
-        <v>-0.0432998329807581</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s">
-        <v>15</v>
-      </c>
-      <c r="B52" t="s">
-        <v>16</v>
-      </c>
-      <c r="C52" t="n">
-        <v>-1.33975368797026</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s">
-        <v>15</v>
-      </c>
-      <c r="B53" t="s">
-        <v>16</v>
-      </c>
-      <c r="C53" t="n">
-        <v>-2.19562414060199</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s">
-        <v>15</v>
-      </c>
-      <c r="B54" t="s">
-        <v>16</v>
-      </c>
-      <c r="C54" t="n">
-        <v>0.496604387441695</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s">
-        <v>15</v>
-      </c>
-      <c r="B55" t="s">
-        <v>16</v>
-      </c>
-      <c r="C55" t="n">
-        <v>-0.394816892068774</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s">
-        <v>15</v>
-      </c>
-      <c r="B56" t="s">
-        <v>16</v>
-      </c>
-      <c r="C56" t="n">
-        <v>-1.64922034801933</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s">
-        <v>15</v>
-      </c>
-      <c r="B57" t="s">
-        <v>16</v>
-      </c>
-      <c r="C57" t="n">
-        <v>-1.99416461717909</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s">
-        <v>15</v>
-      </c>
-      <c r="B58" t="s">
-        <v>16</v>
-      </c>
-      <c r="C58" t="n">
-        <v>-0.579158658807199</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s">
-        <v>15</v>
-      </c>
-      <c r="B59" t="s">
-        <v>16</v>
-      </c>
-      <c r="C59" t="n">
-        <v>-0.62001396211612</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s">
-        <v>15</v>
-      </c>
-      <c r="B60" t="s">
-        <v>16</v>
-      </c>
-      <c r="C60" t="n">
-        <v>-0.977752459944008</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s">
-        <v>15</v>
-      </c>
-      <c r="B61" t="s">
-        <v>16</v>
-      </c>
-      <c r="C61" t="n">
-        <v>0.224691185456911</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s">
-        <v>15</v>
-      </c>
-      <c r="B62" t="s">
-        <v>16</v>
-      </c>
-      <c r="C62" t="n">
-        <v>0.223056648886478</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s">
-        <v>15</v>
-      </c>
-      <c r="B63" t="s">
-        <v>16</v>
-      </c>
-      <c r="C63" t="n">
-        <v>-0.176125565294416</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s">
-        <v>15</v>
-      </c>
-      <c r="B64" t="s">
-        <v>16</v>
-      </c>
-      <c r="C64" t="n">
-        <v>-0.0560824932246275</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s">
-        <v>15</v>
-      </c>
-      <c r="B65" t="s">
-        <v>16</v>
-      </c>
-      <c r="C65" t="n">
-        <v>-1.05266035880272</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s">
-        <v>15</v>
-      </c>
-      <c r="B66" t="s">
-        <v>16</v>
-      </c>
-      <c r="C66" t="n">
-        <v>-0.7396991536346</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s">
-        <v>15</v>
-      </c>
-      <c r="B67" t="s">
-        <v>16</v>
-      </c>
-      <c r="C67" t="n">
-        <v>0.252320267471378</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s">
-        <v>15</v>
-      </c>
-      <c r="B68" t="s">
-        <v>16</v>
-      </c>
-      <c r="C68" t="n">
-        <v>-0.948696100267242</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
-        <v>15</v>
-      </c>
-      <c r="B69" t="s">
-        <v>16</v>
-      </c>
-      <c r="C69" t="n">
-        <v>0.513976395616496</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>15</v>
-      </c>
-      <c r="B70" t="s">
-        <v>16</v>
-      </c>
-      <c r="C70" t="n">
-        <v>-0.118544428661079</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s">
-        <v>15</v>
-      </c>
-      <c r="B71" t="s">
-        <v>16</v>
-      </c>
-      <c r="C71" t="n">
-        <v>-0.345974329386856</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s">
-        <v>15</v>
-      </c>
-      <c r="B72" t="s">
-        <v>16</v>
-      </c>
-      <c r="C72" t="n">
-        <v>-0.483599909861031</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s">
-        <v>15</v>
-      </c>
-      <c r="B73" t="s">
-        <v>16</v>
-      </c>
-      <c r="C73" t="n">
-        <v>-0.6089453815098</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s">
-        <v>15</v>
-      </c>
-      <c r="B74" t="s">
-        <v>16</v>
-      </c>
-      <c r="C74" t="n">
-        <v>-0.482945606150614</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s">
-        <v>15</v>
-      </c>
-      <c r="B75" t="s">
-        <v>16</v>
-      </c>
-      <c r="C75" t="n">
-        <v>-0.153513145403568</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s">
-        <v>15</v>
-      </c>
-      <c r="B76" t="s">
-        <v>16</v>
-      </c>
-      <c r="C76" t="n">
-        <v>-1.57076182158523</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s">
-        <v>15</v>
-      </c>
-      <c r="B77" t="s">
-        <v>16</v>
-      </c>
-      <c r="C77" t="n">
-        <v>-0.303030025610665</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s">
-        <v>15</v>
-      </c>
-      <c r="B78" t="s">
-        <v>16</v>
-      </c>
-      <c r="C78" t="n">
-        <v>-0.885511967714059</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s">
-        <v>15</v>
-      </c>
-      <c r="B79" t="s">
-        <v>16</v>
-      </c>
-      <c r="C79" t="n">
-        <v>-0.655576353593359</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s">
-        <v>15</v>
-      </c>
-      <c r="B80" t="s">
-        <v>16</v>
-      </c>
-      <c r="C80" t="n">
-        <v>-1.49217801521278</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s">
-        <v>15</v>
-      </c>
-      <c r="B81" t="s">
-        <v>16</v>
-      </c>
-      <c r="C81" t="n">
-        <v>-0.279654252422186</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s">
-        <v>15</v>
-      </c>
-      <c r="B82" t="s">
-        <v>16</v>
-      </c>
-      <c r="C82" t="n">
-        <v>-0.926773152668341</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s">
-        <v>15</v>
-      </c>
-      <c r="B83" t="s">
-        <v>16</v>
-      </c>
-      <c r="C83" t="n">
-        <v>-0.370361322654068</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s">
-        <v>15</v>
-      </c>
-      <c r="B84" t="s">
-        <v>16</v>
-      </c>
-      <c r="C84" t="n">
-        <v>-0.918294341525729</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s">
-        <v>15</v>
-      </c>
-      <c r="B85" t="s">
-        <v>16</v>
-      </c>
-      <c r="C85" t="n">
-        <v>0.445132646044803</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s">
-        <v>15</v>
-      </c>
-      <c r="B86" t="s">
-        <v>16</v>
-      </c>
-      <c r="C86" t="n">
-        <v>-0.925977065125412</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s">
-        <v>15</v>
-      </c>
-      <c r="B87" t="s">
-        <v>16</v>
-      </c>
-      <c r="C87" t="n">
-        <v>-1.02121786978119</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s">
-        <v>15</v>
-      </c>
-      <c r="B88" t="s">
-        <v>16</v>
-      </c>
-      <c r="C88" t="n">
-        <v>-1.44646679570741</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s">
-        <v>15</v>
-      </c>
-      <c r="B89" t="s">
-        <v>16</v>
-      </c>
-      <c r="C89" t="n">
-        <v>-1.69536683555342</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s">
-        <v>15</v>
-      </c>
-      <c r="B90" t="s">
-        <v>16</v>
-      </c>
-      <c r="C90" t="n">
-        <v>-0.806157743036711</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s">
-        <v>15</v>
-      </c>
-      <c r="B91" t="s">
-        <v>16</v>
-      </c>
-      <c r="C91" t="n">
-        <v>-0.0540241392829612</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s">
-        <v>15</v>
-      </c>
-      <c r="B92" t="s">
-        <v>16</v>
-      </c>
-      <c r="C92" t="n">
-        <v>-1.4917329122424</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="s">
-        <v>15</v>
-      </c>
-      <c r="B93" t="s">
-        <v>16</v>
-      </c>
-      <c r="C93" t="n">
-        <v>-0.0280047424932794</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s">
-        <v>15</v>
-      </c>
-      <c r="B94" t="s">
-        <v>16</v>
-      </c>
-      <c r="C94" t="n">
-        <v>-1.09587499751673</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s">
-        <v>15</v>
-      </c>
-      <c r="B95" t="s">
-        <v>16</v>
-      </c>
-      <c r="C95" t="n">
-        <v>0.34356274663273</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="s">
-        <v>15</v>
-      </c>
-      <c r="B96" t="s">
-        <v>16</v>
-      </c>
-      <c r="C96" t="n">
-        <v>-0.329038205812318</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="s">
-        <v>15</v>
-      </c>
-      <c r="B97" t="s">
-        <v>16</v>
-      </c>
-      <c r="C97" t="n">
-        <v>-0.221782418557932</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s">
-        <v>15</v>
-      </c>
-      <c r="B98" t="s">
-        <v>16</v>
-      </c>
-      <c r="C98" t="n">
-        <v>-0.982480408745497</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="s">
-        <v>15</v>
-      </c>
-      <c r="B99" t="s">
-        <v>16</v>
-      </c>
-      <c r="C99" t="n">
-        <v>-0.256546583310621</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="s">
-        <v>15</v>
-      </c>
-      <c r="B100" t="s">
-        <v>16</v>
-      </c>
-      <c r="C100" t="n">
-        <v>-0.817309365060069</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s">
-        <v>15</v>
-      </c>
-      <c r="B101" t="s">
-        <v>16</v>
-      </c>
-      <c r="C101" t="n">
-        <v>-0.965251195281235</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s">
-        <v>15</v>
-      </c>
-      <c r="B102" t="s">
-        <v>16</v>
-      </c>
-      <c r="C102" t="n">
-        <v>-0.0452182308141396</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s">
-        <v>15</v>
-      </c>
-      <c r="B103" t="s">
-        <v>16</v>
-      </c>
-      <c r="C103" t="n">
-        <v>-0.484008793451886</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="s">
-        <v>15</v>
-      </c>
-      <c r="B104" t="s">
-        <v>16</v>
-      </c>
-      <c r="C104" t="n">
-        <v>-0.264306425230646</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="s">
-        <v>15</v>
-      </c>
-      <c r="B105" t="s">
-        <v>16</v>
-      </c>
-      <c r="C105" t="n">
-        <v>-0.500249732086173</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="s">
-        <v>15</v>
-      </c>
-      <c r="B106" t="s">
-        <v>16</v>
-      </c>
-      <c r="C106" t="n">
-        <v>-0.461858425235287</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="s">
-        <v>15</v>
-      </c>
-      <c r="B107" t="s">
-        <v>16</v>
-      </c>
-      <c r="C107" t="n">
-        <v>-0.833141814426308</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="s">
-        <v>15</v>
-      </c>
-      <c r="B108" t="s">
-        <v>16</v>
-      </c>
-      <c r="C108" t="n">
-        <v>-0.0156410895843913</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s">
-        <v>15</v>
-      </c>
-      <c r="B109" t="s">
-        <v>16</v>
-      </c>
-      <c r="C109" t="n">
-        <v>-0.295356771306541</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="s">
-        <v>15</v>
-      </c>
-      <c r="B110" t="s">
-        <v>16</v>
-      </c>
-      <c r="C110" t="n">
-        <v>-0.122961286541662</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="s">
-        <v>15</v>
-      </c>
-      <c r="B111" t="s">
-        <v>16</v>
-      </c>
-      <c r="C111" t="n">
-        <v>-2.84559107536646</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="s">
-        <v>15</v>
-      </c>
-      <c r="B112" t="s">
-        <v>16</v>
-      </c>
-      <c r="C112" t="n">
-        <v>-0.869524940905689</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="s">
-        <v>15</v>
-      </c>
-      <c r="B113" t="s">
-        <v>16</v>
-      </c>
-      <c r="C113" t="n">
-        <v>-1.84552645664217</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="s">
-        <v>15</v>
-      </c>
-      <c r="B114" t="s">
-        <v>16</v>
-      </c>
-      <c r="C114" t="n">
-        <v>-1.05579609846763</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="s">
-        <v>15</v>
-      </c>
-      <c r="B115" t="s">
-        <v>16</v>
-      </c>
-      <c r="C115" t="n">
-        <v>-1.41591222851963</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="s">
-        <v>15</v>
-      </c>
-      <c r="B116" t="s">
-        <v>16</v>
-      </c>
-      <c r="C116" t="n">
-        <v>-0.657270351605654</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="s">
-        <v>15</v>
-      </c>
-      <c r="B117" t="s">
-        <v>16</v>
-      </c>
-      <c r="C117" t="n">
-        <v>-0.983989614721039</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="s">
-        <v>15</v>
-      </c>
-      <c r="B118" t="s">
-        <v>16</v>
-      </c>
-      <c r="C118" t="n">
-        <v>-0.477385043899129</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="s">
-        <v>15</v>
-      </c>
-      <c r="B119" t="s">
-        <v>16</v>
-      </c>
-      <c r="C119" t="n">
-        <v>-0.603677138393792</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="s">
-        <v>15</v>
-      </c>
-      <c r="B120" t="s">
-        <v>16</v>
-      </c>
-      <c r="C120" t="n">
-        <v>-0.948625462698641</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="s">
-        <v>15</v>
-      </c>
-      <c r="B121" t="s">
-        <v>16</v>
-      </c>
-      <c r="C121" t="n">
-        <v>0.316995402971687</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="s">
-        <v>15</v>
-      </c>
-      <c r="B122" t="s">
-        <v>16</v>
-      </c>
-      <c r="C122" t="n">
-        <v>-0.767771085085769</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="s">
-        <v>15</v>
-      </c>
-      <c r="B123" t="s">
-        <v>16</v>
-      </c>
-      <c r="C123" t="n">
-        <v>-0.995558015165671</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="s">
-        <v>15</v>
-      </c>
-      <c r="B124" t="s">
-        <v>16</v>
-      </c>
-      <c r="C124" t="n">
-        <v>-0.555280739410548</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="s">
-        <v>15</v>
-      </c>
-      <c r="B125" t="s">
-        <v>16</v>
-      </c>
-      <c r="C125" t="n">
-        <v>0.433469658514964</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="s">
-        <v>15</v>
-      </c>
-      <c r="B126" t="s">
-        <v>16</v>
-      </c>
-      <c r="C126" t="n">
-        <v>-1.50124389005988</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="s">
-        <v>15</v>
-      </c>
-      <c r="B127" t="s">
-        <v>16</v>
-      </c>
-      <c r="C127" t="n">
-        <v>-0.425165314479685</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="s">
-        <v>15</v>
-      </c>
-      <c r="B128" t="s">
-        <v>16</v>
-      </c>
-      <c r="C128" t="n">
-        <v>-0.22666305282826</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="s">
-        <v>15</v>
-      </c>
-      <c r="B129" t="s">
-        <v>16</v>
-      </c>
-      <c r="C129" t="n">
-        <v>0.052058089870159</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="s">
-        <v>15</v>
-      </c>
-      <c r="B130" t="s">
-        <v>16</v>
-      </c>
-      <c r="C130" t="n">
-        <v>-0.207197809639708</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="s">
-        <v>15</v>
-      </c>
-      <c r="B131" t="s">
-        <v>16</v>
-      </c>
-      <c r="C131" t="n">
-        <v>-0.60457159001127</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="s">
-        <v>15</v>
-      </c>
-      <c r="B132" t="s">
-        <v>16</v>
-      </c>
-      <c r="C132" t="n">
-        <v>-0.152031223425119</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="s">
-        <v>15</v>
-      </c>
-      <c r="B133" t="s">
-        <v>16</v>
-      </c>
-      <c r="C133" t="n">
-        <v>-0.648878134950069</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="s">
-        <v>15</v>
-      </c>
-      <c r="B134" t="s">
-        <v>16</v>
-      </c>
-      <c r="C134" t="n">
-        <v>-0.0882713951591105</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="s">
-        <v>15</v>
-      </c>
-      <c r="B135" t="s">
-        <v>16</v>
-      </c>
-      <c r="C135" t="n">
-        <v>-0.335816955295595</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="s">
-        <v>15</v>
-      </c>
-      <c r="B136" t="s">
-        <v>16</v>
-      </c>
-      <c r="C136" t="n">
-        <v>-0.181720581697174</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="s">
-        <v>15</v>
-      </c>
-      <c r="B137" t="s">
-        <v>16</v>
-      </c>
-      <c r="C137" t="n">
-        <v>-0.34815268044666</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="s">
-        <v>15</v>
-      </c>
-      <c r="B138" t="s">
-        <v>16</v>
-      </c>
-      <c r="C138" t="n">
-        <v>-0.312500310512463</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="s">
-        <v>15</v>
-      </c>
-      <c r="B139" t="s">
-        <v>16</v>
-      </c>
-      <c r="C139" t="n">
-        <v>-0.324163757861141</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="s">
-        <v>15</v>
-      </c>
-      <c r="B140" t="s">
-        <v>16</v>
-      </c>
-      <c r="C140" t="n">
-        <v>-1.03027530675682</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="s">
-        <v>15</v>
-      </c>
-      <c r="B141" t="s">
-        <v>16</v>
-      </c>
-      <c r="C141" t="n">
-        <v>-0.890041780844972</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="s">
-        <v>15</v>
-      </c>
-      <c r="B142" t="s">
-        <v>16</v>
-      </c>
-      <c r="C142" t="n">
-        <v>-0.0637316173232727</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="s">
-        <v>15</v>
-      </c>
-      <c r="B143" t="s">
-        <v>16</v>
-      </c>
-      <c r="C143" t="n">
-        <v>-0.265313979155819</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="s">
-        <v>15</v>
-      </c>
-      <c r="B144" t="s">
-        <v>16</v>
-      </c>
-      <c r="C144" t="n">
-        <v>-1.28012293591064</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="s">
-        <v>15</v>
-      </c>
-      <c r="B145" t="s">
-        <v>16</v>
-      </c>
-      <c r="C145" t="n">
-        <v>0.0513878651479989</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="s">
-        <v>15</v>
-      </c>
-      <c r="B146" t="s">
-        <v>16</v>
-      </c>
-      <c r="C146" t="n">
-        <v>-0.452959124949998</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="s">
-        <v>15</v>
-      </c>
-      <c r="B147" t="s">
-        <v>16</v>
-      </c>
-      <c r="C147" t="n">
-        <v>-0.56119010309012</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="s">
-        <v>15</v>
-      </c>
-      <c r="B148" t="s">
-        <v>16</v>
-      </c>
-      <c r="C148" t="n">
-        <v>-0.188333472347131</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="s">
-        <v>15</v>
-      </c>
-      <c r="B149" t="s">
-        <v>16</v>
-      </c>
-      <c r="C149" t="n">
-        <v>0.529579627513525</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="s">
-        <v>15</v>
-      </c>
-      <c r="B150" t="s">
-        <v>16</v>
-      </c>
-      <c r="C150" t="n">
-        <v>-0.175768299760764</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="s">
-        <v>15</v>
-      </c>
-      <c r="B151" t="s">
-        <v>16</v>
-      </c>
-      <c r="C151" t="n">
-        <v>-0.716292424674719</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="s">
-        <v>15</v>
-      </c>
-      <c r="B152" t="s">
-        <v>16</v>
-      </c>
-      <c r="C152" t="n">
-        <v>-1.1950888910032</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="s">
-        <v>15</v>
-      </c>
-      <c r="B153" t="s">
-        <v>16</v>
-      </c>
-      <c r="C153" t="n">
-        <v>-3.80653217365739</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="s">
-        <v>15</v>
-      </c>
-      <c r="B154" t="s">
-        <v>16</v>
-      </c>
-      <c r="C154" t="n">
-        <v>-0.314997355639064</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="s">
-        <v>15</v>
-      </c>
-      <c r="B155" t="s">
-        <v>16</v>
-      </c>
-      <c r="C155" t="n">
-        <v>-0.759919799246453</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="s">
-        <v>15</v>
-      </c>
-      <c r="B156" t="s">
-        <v>16</v>
-      </c>
-      <c r="C156" t="n">
-        <v>-0.306270667907784</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="s">
-        <v>15</v>
-      </c>
-      <c r="B157" t="s">
-        <v>16</v>
-      </c>
-      <c r="C157" t="n">
-        <v>-0.356088566318354</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="s">
-        <v>15</v>
-      </c>
-      <c r="B158" t="s">
-        <v>16</v>
-      </c>
-      <c r="C158" t="n">
-        <v>-0.666692567058941</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="s">
-        <v>15</v>
-      </c>
-      <c r="B159" t="s">
-        <v>16</v>
-      </c>
-      <c r="C159" t="n">
-        <v>-0.409672501166556</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s">
-        <v>15</v>
-      </c>
-      <c r="B160" t="s">
-        <v>16</v>
-      </c>
-      <c r="C160" t="n">
-        <v>-0.329362612330978</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="s">
-        <v>15</v>
-      </c>
-      <c r="B161" t="s">
-        <v>16</v>
-      </c>
-      <c r="C161" t="n">
-        <v>-0.551079410468758</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="s">
-        <v>15</v>
-      </c>
-      <c r="B162" t="s">
-        <v>16</v>
-      </c>
-      <c r="C162" t="n">
-        <v>-0.647404975852356</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="s">
-        <v>15</v>
-      </c>
-      <c r="B163" t="s">
-        <v>16</v>
-      </c>
-      <c r="C163" t="n">
-        <v>-0.66564970249272</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="s">
-        <v>15</v>
-      </c>
-      <c r="B164" t="s">
-        <v>16</v>
-      </c>
-      <c r="C164" t="n">
-        <v>-0.386247200631508</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="s">
-        <v>15</v>
-      </c>
-      <c r="B165" t="s">
-        <v>16</v>
-      </c>
-      <c r="C165" t="n">
-        <v>-0.513651148028589</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="s">
-        <v>15</v>
-      </c>
-      <c r="B166" t="s">
-        <v>16</v>
-      </c>
-      <c r="C166" t="n">
-        <v>-1.50766356240402</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="s">
-        <v>15</v>
-      </c>
-      <c r="B167" t="s">
-        <v>16</v>
-      </c>
-      <c r="C167" t="n">
-        <v>-1.70155742511712</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="s">
-        <v>15</v>
-      </c>
-      <c r="B168" t="s">
-        <v>16</v>
-      </c>
-      <c r="C168" t="n">
-        <v>-0.986704690964469</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="s">
-        <v>15</v>
-      </c>
-      <c r="B169" t="s">
-        <v>16</v>
-      </c>
-      <c r="C169" t="n">
-        <v>-0.0405309077445823</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="s">
-        <v>15</v>
-      </c>
-      <c r="B170" t="s">
-        <v>16</v>
-      </c>
-      <c r="C170" t="n">
-        <v>-0.31837664785437</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="s">
-        <v>15</v>
-      </c>
-      <c r="B171" t="s">
-        <v>16</v>
-      </c>
-      <c r="C171" t="n">
-        <v>-0.0342808020242591</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="s">
-        <v>15</v>
-      </c>
-      <c r="B172" t="s">
-        <v>16</v>
-      </c>
-      <c r="C172" t="n">
-        <v>-0.0569993896079428</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="s">
-        <v>15</v>
-      </c>
-      <c r="B173" t="s">
-        <v>16</v>
-      </c>
-      <c r="C173" t="n">
-        <v>-0.804211781324568</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="s">
-        <v>15</v>
-      </c>
-      <c r="B174" t="s">
-        <v>16</v>
-      </c>
-      <c r="C174" t="n">
-        <v>-0.528518844826253</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="s">
-        <v>15</v>
-      </c>
-      <c r="B175" t="s">
-        <v>16</v>
-      </c>
-      <c r="C175" t="n">
-        <v>-0.491338271665452</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="s">
-        <v>15</v>
-      </c>
-      <c r="B176" t="s">
-        <v>16</v>
-      </c>
-      <c r="C176" t="n">
-        <v>-0.832632977899181</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="s">
-        <v>15</v>
-      </c>
-      <c r="B177" t="s">
-        <v>16</v>
-      </c>
-      <c r="C177" t="n">
-        <v>-0.313862334558564</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="s">
-        <v>15</v>
-      </c>
-      <c r="B178" t="s">
-        <v>16</v>
-      </c>
-      <c r="C178" t="n">
-        <v>-1.20475671085629</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="s">
-        <v>15</v>
-      </c>
-      <c r="B179" t="s">
-        <v>16</v>
-      </c>
-      <c r="C179" t="n">
-        <v>-0.148184882584399</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="s">
-        <v>15</v>
-      </c>
-      <c r="B180" t="s">
-        <v>16</v>
-      </c>
-      <c r="C180" t="n">
-        <v>-0.0851266505993973</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="s">
-        <v>15</v>
-      </c>
-      <c r="B181" t="s">
-        <v>16</v>
-      </c>
-      <c r="C181" t="n">
-        <v>0.670921076444561</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="s">
-        <v>15</v>
-      </c>
-      <c r="B182" t="s">
-        <v>16</v>
-      </c>
-      <c r="C182" t="n">
-        <v>0.155036608393653</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="s">
-        <v>15</v>
-      </c>
-      <c r="B183" t="s">
-        <v>16</v>
-      </c>
-      <c r="C183" t="n">
-        <v>-1.79577366888049</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="s">
-        <v>15</v>
-      </c>
-      <c r="B184" t="s">
-        <v>16</v>
-      </c>
-      <c r="C184" t="n">
-        <v>0.198540638391973</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="s">
-        <v>15</v>
-      </c>
-      <c r="B185" t="s">
-        <v>16</v>
-      </c>
-      <c r="C185" t="n">
-        <v>-1.15665548962788</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="s">
-        <v>15</v>
-      </c>
-      <c r="B186" t="s">
-        <v>16</v>
-      </c>
-      <c r="C186" t="n">
-        <v>-1.56385935136295</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="s">
-        <v>15</v>
-      </c>
-      <c r="B187" t="s">
-        <v>16</v>
-      </c>
-      <c r="C187" t="n">
-        <v>-0.991664265077138</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="s">
-        <v>15</v>
-      </c>
-      <c r="B188" t="s">
-        <v>16</v>
-      </c>
-      <c r="C188" t="n">
-        <v>-0.622905238059787</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="s">
-        <v>15</v>
-      </c>
-      <c r="B189" t="s">
-        <v>16</v>
-      </c>
-      <c r="C189" t="n">
-        <v>-0.614695099879471</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="s">
-        <v>15</v>
-      </c>
-      <c r="B190" t="s">
-        <v>16</v>
-      </c>
-      <c r="C190" t="n">
-        <v>-0.540223283797587</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="s">
-        <v>15</v>
-      </c>
-      <c r="B191" t="s">
-        <v>16</v>
-      </c>
-      <c r="C191" t="n">
-        <v>-0.705499317049483</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="s">
-        <v>15</v>
-      </c>
-      <c r="B192" t="s">
-        <v>16</v>
-      </c>
-      <c r="C192" t="n">
-        <v>-1.00478385801305</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="s">
-        <v>15</v>
-      </c>
-      <c r="B193" t="s">
-        <v>16</v>
-      </c>
-      <c r="C193" t="n">
-        <v>-0.811982182184559</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="s">
-        <v>15</v>
-      </c>
-      <c r="B194" t="s">
-        <v>16</v>
-      </c>
-      <c r="C194" t="n">
-        <v>-0.957555308873622</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="s">
-        <v>15</v>
-      </c>
-      <c r="B195" t="s">
-        <v>16</v>
-      </c>
-      <c r="C195" t="n">
-        <v>-0.712843200192879</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="s">
-        <v>15</v>
-      </c>
-      <c r="B196" t="s">
-        <v>16</v>
-      </c>
-      <c r="C196" t="n">
-        <v>-0.13886303898786</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="s">
-        <v>15</v>
-      </c>
-      <c r="B197" t="s">
-        <v>16</v>
-      </c>
-      <c r="C197" t="n">
-        <v>-0.668835451386937</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="s">
-        <v>15</v>
-      </c>
-      <c r="B198" t="s">
-        <v>16</v>
-      </c>
-      <c r="C198" t="n">
-        <v>-0.672936767333097</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="s">
-        <v>15</v>
-      </c>
-      <c r="B199" t="s">
-        <v>16</v>
-      </c>
-      <c r="C199" t="n">
-        <v>-0.99208447018957</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="s">
-        <v>15</v>
-      </c>
-      <c r="B200" t="s">
-        <v>16</v>
-      </c>
-      <c r="C200" t="n">
-        <v>-0.197264484858048</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="s">
-        <v>15</v>
-      </c>
-      <c r="B201" t="s">
-        <v>16</v>
-      </c>
-      <c r="C201" t="n">
-        <v>-0.322591597808607</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -3286,7 +1099,7 @@
         <v>1.706</v>
       </c>
       <c r="E2" t="n">
-        <v>0.675284045923149</v>
+        <v>1.31597453767446</v>
       </c>
     </row>
     <row r="3">
@@ -3303,7 +1116,7 @@
         <v>4.218</v>
       </c>
       <c r="E3" t="n">
-        <v>1.56760217532446</v>
+        <v>1.48016853941018</v>
       </c>
     </row>
     <row r="4">
@@ -3320,7 +1133,7 @@
         <v>1.578</v>
       </c>
       <c r="E4" t="n">
-        <v>1.47442806772498</v>
+        <v>0.974667128884759</v>
       </c>
     </row>
     <row r="5">
@@ -3337,7 +1150,7 @@
         <v>3.683</v>
       </c>
       <c r="E5" t="n">
-        <v>3.25053913997298</v>
+        <v>3.45546803903723</v>
       </c>
     </row>
     <row r="6">
@@ -3354,7 +1167,7 @@
         <v>2.983</v>
       </c>
       <c r="E6" t="n">
-        <v>1.84754095666717</v>
+        <v>1.90011159418757</v>
       </c>
     </row>
     <row r="7">
@@ -3371,7 +1184,7 @@
         <v>2.44</v>
       </c>
       <c r="E7" t="n">
-        <v>3.66664655857035</v>
+        <v>3.67606607062664</v>
       </c>
     </row>
     <row r="8">
@@ -3388,7 +1201,7 @@
         <v>3.614</v>
       </c>
       <c r="E8" t="n">
-        <v>0.766522491720189</v>
+        <v>0.652217682895701</v>
       </c>
     </row>
     <row r="9">
@@ -3405,7 +1218,7 @@
         <v>0.579999999999998</v>
       </c>
       <c r="E9" t="n">
-        <v>2.76992241909426</v>
+        <v>2.77438054729018</v>
       </c>
     </row>
     <row r="10">
@@ -3422,7 +1235,7 @@
         <v>-1.918</v>
       </c>
       <c r="E10" t="n">
-        <v>1.94322490409938</v>
+        <v>1.90529002432802</v>
       </c>
     </row>
     <row r="11">
@@ -3439,7 +1252,7 @@
         <v>0.672000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>1.22139734771122</v>
+        <v>1.19812351398515</v>
       </c>
     </row>
     <row r="12">
@@ -3456,7 +1269,7 @@
         <v>0.352999999999998</v>
       </c>
       <c r="E12" t="n">
-        <v>0.750856387391998</v>
+        <v>0.652555538816786</v>
       </c>
     </row>
     <row r="13">
@@ -3473,7 +1286,7 @@
         <v>5.08900000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>1.81798705801732</v>
+        <v>1.86654037826459</v>
       </c>
     </row>
     <row r="14">
@@ -3490,7 +1303,7 @@
         <v>0.181000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>2.54947120836145</v>
+        <v>2.48742924973582</v>
       </c>
     </row>
     <row r="15">
@@ -3507,7 +1320,7 @@
         <v>1.311</v>
       </c>
       <c r="E15" t="n">
-        <v>1.31021319020451</v>
+        <v>1.22975739275684</v>
       </c>
     </row>
     <row r="16">
@@ -3524,7 +1337,7 @@
         <v>2.862</v>
       </c>
       <c r="E16" t="n">
-        <v>1.95465267705218</v>
+        <v>1.93527503493478</v>
       </c>
     </row>
   </sheetData>
@@ -3634,10 +1447,10 @@
         <v>42</v>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>0.866666666666667</v>
+        <v>0.933333333333333</v>
       </c>
     </row>
     <row r="7">
@@ -3651,10 +1464,10 @@
         <v>43</v>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>0.866666666666667</v>
+        <v>0.933333333333333</v>
       </c>
     </row>
     <row r="8">
@@ -3668,10 +1481,10 @@
         <v>44</v>
       </c>
       <c r="D8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E8" t="n">
-        <v>0.866666666666667</v>
+        <v>0.933333333333333</v>
       </c>
     </row>
     <row r="9">
@@ -3685,10 +1498,10 @@
         <v>45</v>
       </c>
       <c r="D9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E9" t="n">
-        <v>0.866666666666667</v>
+        <v>0.933333333333333</v>
       </c>
     </row>
     <row r="10">
@@ -3702,10 +1515,10 @@
         <v>46</v>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8</v>
+        <v>0.933333333333333</v>
       </c>
     </row>
     <row r="11">
@@ -3719,10 +1532,10 @@
         <v>47</v>
       </c>
       <c r="D11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8</v>
+        <v>0.933333333333333</v>
       </c>
     </row>
     <row r="12">
@@ -3736,10 +1549,10 @@
         <v>48</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E12" t="n">
-        <v>0.666666666666667</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="13">
@@ -3753,10 +1566,10 @@
         <v>49</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E13" t="n">
-        <v>0.666666666666667</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="14">
@@ -3770,10 +1583,10 @@
         <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E14" t="n">
-        <v>0.666666666666667</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="15">
@@ -3787,10 +1600,10 @@
         <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E15" t="n">
-        <v>0.666666666666667</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="16">
@@ -3804,10 +1617,10 @@
         <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E16" t="n">
-        <v>0.666666666666667</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="17">
@@ -3821,10 +1634,10 @@
         <v>53</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="18">
@@ -3838,10 +1651,10 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="19">
@@ -3855,10 +1668,10 @@
         <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="20">
@@ -3872,10 +1685,10 @@
         <v>56</v>
       </c>
       <c r="D20" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="21">
@@ -3889,10 +1702,10 @@
         <v>57</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E21" t="n">
-        <v>0.533333333333333</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="22">
@@ -3906,10 +1719,10 @@
         <v>58</v>
       </c>
       <c r="D22" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E22" t="n">
-        <v>0.533333333333333</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="23">
@@ -3923,10 +1736,10 @@
         <v>59</v>
       </c>
       <c r="D23" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E23" t="n">
-        <v>0.533333333333333</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="24">
@@ -3940,10 +1753,10 @@
         <v>60</v>
       </c>
       <c r="D24" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E24" t="n">
-        <v>0.533333333333333</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="25">
@@ -3957,10 +1770,10 @@
         <v>61</v>
       </c>
       <c r="D25" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E25" t="n">
-        <v>0.533333333333333</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="26">
@@ -3974,10 +1787,10 @@
         <v>62</v>
       </c>
       <c r="D26" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E26" t="n">
-        <v>0.466666666666667</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="27">
@@ -3991,10 +1804,10 @@
         <v>63</v>
       </c>
       <c r="D27" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E27" t="n">
-        <v>0.466666666666667</v>
+        <v>0.733333333333333</v>
       </c>
     </row>
     <row r="28">
@@ -4008,10 +1821,10 @@
         <v>64</v>
       </c>
       <c r="D28" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E28" t="n">
-        <v>0.466666666666667</v>
+        <v>0.733333333333333</v>
       </c>
     </row>
     <row r="29">
@@ -4025,10 +1838,10 @@
         <v>65</v>
       </c>
       <c r="D29" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E29" t="n">
-        <v>0.466666666666667</v>
+        <v>0.733333333333333</v>
       </c>
     </row>
     <row r="30">
@@ -4042,10 +1855,10 @@
         <v>66</v>
       </c>
       <c r="D30" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E30" t="n">
-        <v>0.466666666666667</v>
+        <v>0.733333333333333</v>
       </c>
     </row>
     <row r="31">
@@ -4059,10 +1872,10 @@
         <v>67</v>
       </c>
       <c r="D31" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E31" t="n">
-        <v>0.466666666666667</v>
+        <v>0.733333333333333</v>
       </c>
     </row>
     <row r="32">
@@ -4076,10 +1889,10 @@
         <v>68</v>
       </c>
       <c r="D32" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E32" t="n">
-        <v>0.466666666666667</v>
+        <v>0.733333333333333</v>
       </c>
     </row>
     <row r="33">
@@ -4093,10 +1906,10 @@
         <v>69</v>
       </c>
       <c r="D33" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E33" t="n">
-        <v>0.466666666666667</v>
+        <v>0.733333333333333</v>
       </c>
     </row>
     <row r="34">
@@ -4110,10 +1923,10 @@
         <v>70</v>
       </c>
       <c r="D34" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E34" t="n">
-        <v>0.466666666666667</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="35">
@@ -4127,10 +1940,10 @@
         <v>71</v>
       </c>
       <c r="D35" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E35" t="n">
-        <v>0.4</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="36">
@@ -4144,10 +1957,10 @@
         <v>72</v>
       </c>
       <c r="D36" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E36" t="n">
-        <v>0.4</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="37">
@@ -4161,10 +1974,10 @@
         <v>73</v>
       </c>
       <c r="D37" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E37" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="38">
@@ -4178,10 +1991,10 @@
         <v>74</v>
       </c>
       <c r="D38" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E38" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="39">
@@ -4195,10 +2008,10 @@
         <v>75</v>
       </c>
       <c r="D39" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E39" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="40">
@@ -4212,10 +2025,10 @@
         <v>76</v>
       </c>
       <c r="D40" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E40" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="41">
@@ -4229,10 +2042,10 @@
         <v>77</v>
       </c>
       <c r="D41" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E41" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="42">
@@ -4246,10 +2059,10 @@
         <v>78</v>
       </c>
       <c r="D42" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E42" t="n">
-        <v>0.333333333333333</v>
+        <v>0.533333333333333</v>
       </c>
     </row>
     <row r="43">
@@ -4263,10 +2076,10 @@
         <v>79</v>
       </c>
       <c r="D43" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E43" t="n">
-        <v>0.333333333333333</v>
+        <v>0.533333333333333</v>
       </c>
     </row>
     <row r="44">
@@ -4280,10 +2093,10 @@
         <v>80</v>
       </c>
       <c r="D44" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E44" t="n">
-        <v>0.266666666666667</v>
+        <v>0.466666666666667</v>
       </c>
     </row>
     <row r="45">
@@ -4297,10 +2110,10 @@
         <v>81</v>
       </c>
       <c r="D45" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E45" t="n">
-        <v>0.266666666666667</v>
+        <v>0.466666666666667</v>
       </c>
     </row>
     <row r="46">
@@ -4314,10 +2127,10 @@
         <v>82</v>
       </c>
       <c r="D46" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E46" t="n">
-        <v>0.266666666666667</v>
+        <v>0.466666666666667</v>
       </c>
     </row>
     <row r="47">
@@ -4331,10 +2144,10 @@
         <v>83</v>
       </c>
       <c r="D47" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E47" t="n">
-        <v>0.266666666666667</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="48">
@@ -4348,10 +2161,10 @@
         <v>84</v>
       </c>
       <c r="D48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E48" t="n">
-        <v>0.2</v>
+        <v>0.266666666666667</v>
       </c>
     </row>
     <row r="49">
@@ -4365,10 +2178,10 @@
         <v>85</v>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E49" t="n">
-        <v>0.2</v>
+        <v>0.266666666666667</v>
       </c>
     </row>
     <row r="50">
@@ -4382,10 +2195,10 @@
         <v>86</v>
       </c>
       <c r="D50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E50" t="n">
-        <v>0.2</v>
+        <v>0.266666666666667</v>
       </c>
     </row>
     <row r="51">
@@ -4399,10 +2212,10 @@
         <v>87</v>
       </c>
       <c r="D51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E51" t="n">
-        <v>0.2</v>
+        <v>0.266666666666667</v>
       </c>
     </row>
     <row r="52">
@@ -4416,10 +2229,10 @@
         <v>88</v>
       </c>
       <c r="D52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>0.133333333333333</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="53">
@@ -4433,10 +2246,10 @@
         <v>89</v>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E53" t="n">
-        <v>0.133333333333333</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="54">
@@ -4450,10 +2263,10 @@
         <v>90</v>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E54" t="n">
-        <v>0.133333333333333</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="55">
@@ -4467,10 +2280,10 @@
         <v>91</v>
       </c>
       <c r="D55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>0.133333333333333</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="56">
@@ -4484,10 +2297,10 @@
         <v>92</v>
       </c>
       <c r="D56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E56" t="n">
-        <v>0.133333333333333</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="57">
@@ -4501,10 +2314,10 @@
         <v>93</v>
       </c>
       <c r="D57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E57" t="n">
-        <v>0.133333333333333</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="58">
@@ -4705,10 +2518,10 @@
         <v>105</v>
       </c>
       <c r="D69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="70">
@@ -4722,10 +2535,10 @@
         <v>106</v>
       </c>
       <c r="D70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E70" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="71">
@@ -4739,10 +2552,10 @@
         <v>107</v>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E71" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="72">
@@ -4756,10 +2569,10 @@
         <v>108</v>
       </c>
       <c r="D72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="73">
@@ -4773,10 +2586,10 @@
         <v>109</v>
       </c>
       <c r="D73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E73" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="74">
@@ -4790,10 +2603,10 @@
         <v>110</v>
       </c>
       <c r="D74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E74" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="75">
@@ -6102,6 +3915,125 @@
         <v>1</v>
       </c>
       <c r="E151" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" t="s">
+        <v>16</v>
+      </c>
+      <c r="C152" t="s">
+        <v>188</v>
+      </c>
+      <c r="D152" t="n">
+        <v>1</v>
+      </c>
+      <c r="E152" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>15</v>
+      </c>
+      <c r="B153" t="s">
+        <v>16</v>
+      </c>
+      <c r="C153" t="s">
+        <v>189</v>
+      </c>
+      <c r="D153" t="n">
+        <v>1</v>
+      </c>
+      <c r="E153" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>15</v>
+      </c>
+      <c r="B154" t="s">
+        <v>16</v>
+      </c>
+      <c r="C154" t="s">
+        <v>190</v>
+      </c>
+      <c r="D154" t="n">
+        <v>1</v>
+      </c>
+      <c r="E154" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>15</v>
+      </c>
+      <c r="B155" t="s">
+        <v>16</v>
+      </c>
+      <c r="C155" t="s">
+        <v>191</v>
+      </c>
+      <c r="D155" t="n">
+        <v>1</v>
+      </c>
+      <c r="E155" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>15</v>
+      </c>
+      <c r="B156" t="s">
+        <v>16</v>
+      </c>
+      <c r="C156" t="s">
+        <v>192</v>
+      </c>
+      <c r="D156" t="n">
+        <v>1</v>
+      </c>
+      <c r="E156" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>15</v>
+      </c>
+      <c r="B157" t="s">
+        <v>16</v>
+      </c>
+      <c r="C157" t="s">
+        <v>193</v>
+      </c>
+      <c r="D157" t="n">
+        <v>1</v>
+      </c>
+      <c r="E157" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>15</v>
+      </c>
+      <c r="B158" t="s">
+        <v>16</v>
+      </c>
+      <c r="C158" t="s">
+        <v>194</v>
+      </c>
+      <c r="D158" t="n">
+        <v>1</v>
+      </c>
+      <c r="E158" t="n">
         <v>0.0666666666666667</v>
       </c>
     </row>

--- a/05_Figures/F06_prediction/proteins/T1/d_mcsa/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/T1/d_mcsa/spls/c_data/results.xlsx
@@ -1022,7 +1022,7 @@
         <v>1898</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H3" t="n">
         <v>-0.172867637882008</v>
@@ -1030,10 +1030,18 @@
       <c r="I3" t="n">
         <v>0.025</v>
       </c>
-      <c r="J3"/>
-      <c r="K3"/>
-      <c r="L3"/>
-      <c r="M3"/>
+      <c r="J3" t="n">
+        <v>0.213930348258706</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.412935323383085</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.590123508304156</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.550735857757619</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1057,6 +1065,2206 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.604135525631475</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.837361772709086</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-1.32357069023878</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.285597321803156</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.787710528085295</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.83948764904375</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.722390858730737</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.0706835109044527</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.309321438903778</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-1.16650819176273</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.460820690780944</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.058892042818421</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.510640755861641</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.136758512290286</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.36092821369293</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.661946437185221</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.370306162282434</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-1.26673543225489</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-0.843340129103183</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-0.292232575673052</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-0.676988139476345</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.0300220212246954</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.229608627080297</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-1.88301401727437</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="n">
+        <v>-0.249279463222961</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-0.904916402764228</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" t="n">
+        <v>-1.53421530524201</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.0801919201982336</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-0.263073587765471</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" t="n">
+        <v>-0.871806526994566</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.244173665739194</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-0.569538554001737</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-0.20226146007521</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" t="n">
+        <v>-0.5379963231359</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.0632724088620403</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-0.583554713593295</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-1.0501605134861</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-0.0761209725776542</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" t="n">
+        <v>-1.05648075692822</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" t="n">
+        <v>-0.703364160243351</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" t="n">
+        <v>-0.748811820929309</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" t="n">
+        <v>-0.310403097152448</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" t="n">
+        <v>-0.261756076933068</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" t="n">
+        <v>-0.482281325212605</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" t="n">
+        <v>-0.45907820628261</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" t="n">
+        <v>-0.131538020566747</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>15</v>
+      </c>
+      <c r="B48" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" t="n">
+        <v>-0.503342468673799</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" t="n">
+        <v>-1.35066772811912</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.303893921254062</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" t="n">
+        <v>-0.0516716678200402</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52" t="n">
+        <v>-1.41331171543701</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53" t="s">
+        <v>16</v>
+      </c>
+      <c r="C53" t="n">
+        <v>-1.41584586140855</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>15</v>
+      </c>
+      <c r="B54" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.0959193772181903</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" t="n">
+        <v>-0.459857748828053</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" t="n">
+        <v>-1.9260516173741</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>15</v>
+      </c>
+      <c r="B57" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" t="n">
+        <v>-1.6629509402579</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>15</v>
+      </c>
+      <c r="B58" t="s">
+        <v>16</v>
+      </c>
+      <c r="C58" t="n">
+        <v>-0.400628727858785</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" t="n">
+        <v>-0.506399806631758</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>15</v>
+      </c>
+      <c r="B60" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" t="n">
+        <v>-0.983819069333065</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61" t="n">
+        <v>-0.0275474278627543</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>15</v>
+      </c>
+      <c r="B62" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0.147078537506649</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>15</v>
+      </c>
+      <c r="B63" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63" t="n">
+        <v>-0.619342550345187</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>15</v>
+      </c>
+      <c r="B64" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" t="n">
+        <v>-0.296533148499641</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>15</v>
+      </c>
+      <c r="B65" t="s">
+        <v>16</v>
+      </c>
+      <c r="C65" t="n">
+        <v>-0.746806810677365</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>15</v>
+      </c>
+      <c r="B66" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" t="n">
+        <v>-0.769839025503791</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>15</v>
+      </c>
+      <c r="B67" t="s">
+        <v>16</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0.20433958122484</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>15</v>
+      </c>
+      <c r="B68" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" t="n">
+        <v>-1.15559087413182</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>15</v>
+      </c>
+      <c r="B69" t="s">
+        <v>16</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0.439610349468085</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>15</v>
+      </c>
+      <c r="B70" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" t="n">
+        <v>-0.209738494893384</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>15</v>
+      </c>
+      <c r="B71" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" t="n">
+        <v>-0.413943608569793</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>15</v>
+      </c>
+      <c r="B72" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" t="n">
+        <v>-0.588593410893849</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>15</v>
+      </c>
+      <c r="B73" t="s">
+        <v>16</v>
+      </c>
+      <c r="C73" t="n">
+        <v>-0.61538891859357</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>15</v>
+      </c>
+      <c r="B74" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" t="n">
+        <v>-0.710399997145806</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>15</v>
+      </c>
+      <c r="B75" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" t="n">
+        <v>-0.0702690740006939</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>15</v>
+      </c>
+      <c r="B76" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" t="n">
+        <v>-1.55662824476677</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>15</v>
+      </c>
+      <c r="B77" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" t="n">
+        <v>-0.352871097988165</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>15</v>
+      </c>
+      <c r="B78" t="s">
+        <v>16</v>
+      </c>
+      <c r="C78" t="n">
+        <v>-1.04981520536555</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>15</v>
+      </c>
+      <c r="B79" t="s">
+        <v>16</v>
+      </c>
+      <c r="C79" t="n">
+        <v>-0.735467820380805</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>15</v>
+      </c>
+      <c r="B80" t="s">
+        <v>16</v>
+      </c>
+      <c r="C80" t="n">
+        <v>-1.68590591198902</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>15</v>
+      </c>
+      <c r="B81" t="s">
+        <v>16</v>
+      </c>
+      <c r="C81" t="n">
+        <v>-0.620876686140593</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>15</v>
+      </c>
+      <c r="B82" t="s">
+        <v>16</v>
+      </c>
+      <c r="C82" t="n">
+        <v>-0.727714161700143</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>15</v>
+      </c>
+      <c r="B83" t="s">
+        <v>16</v>
+      </c>
+      <c r="C83" t="n">
+        <v>-0.393516794834228</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>15</v>
+      </c>
+      <c r="B84" t="s">
+        <v>16</v>
+      </c>
+      <c r="C84" t="n">
+        <v>-0.947917618854295</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>15</v>
+      </c>
+      <c r="B85" t="s">
+        <v>16</v>
+      </c>
+      <c r="C85" t="n">
+        <v>0.440697982699365</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>15</v>
+      </c>
+      <c r="B86" t="s">
+        <v>16</v>
+      </c>
+      <c r="C86" t="n">
+        <v>-0.77542058735957</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>15</v>
+      </c>
+      <c r="B87" t="s">
+        <v>16</v>
+      </c>
+      <c r="C87" t="n">
+        <v>-0.695784982960008</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>15</v>
+      </c>
+      <c r="B88" t="s">
+        <v>16</v>
+      </c>
+      <c r="C88" t="n">
+        <v>-1.23699101111082</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>15</v>
+      </c>
+      <c r="B89" t="s">
+        <v>16</v>
+      </c>
+      <c r="C89" t="n">
+        <v>-1.65718831626801</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>15</v>
+      </c>
+      <c r="B90" t="s">
+        <v>16</v>
+      </c>
+      <c r="C90" t="n">
+        <v>-0.904813194217462</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>15</v>
+      </c>
+      <c r="B91" t="s">
+        <v>16</v>
+      </c>
+      <c r="C91" t="n">
+        <v>-0.0509143814912072</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>15</v>
+      </c>
+      <c r="B92" t="s">
+        <v>16</v>
+      </c>
+      <c r="C92" t="n">
+        <v>-1.33141132314255</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>15</v>
+      </c>
+      <c r="B93" t="s">
+        <v>16</v>
+      </c>
+      <c r="C93" t="n">
+        <v>-0.0561224815047956</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>15</v>
+      </c>
+      <c r="B94" t="s">
+        <v>16</v>
+      </c>
+      <c r="C94" t="n">
+        <v>-0.841483168323061</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>15</v>
+      </c>
+      <c r="B95" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0.379073322895043</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>15</v>
+      </c>
+      <c r="B96" t="s">
+        <v>16</v>
+      </c>
+      <c r="C96" t="n">
+        <v>-0.359518024090856</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>15</v>
+      </c>
+      <c r="B97" t="s">
+        <v>16</v>
+      </c>
+      <c r="C97" t="n">
+        <v>-0.260837405584045</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>15</v>
+      </c>
+      <c r="B98" t="s">
+        <v>16</v>
+      </c>
+      <c r="C98" t="n">
+        <v>-0.880828715517086</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>15</v>
+      </c>
+      <c r="B99" t="s">
+        <v>16</v>
+      </c>
+      <c r="C99" t="n">
+        <v>-0.207450216110295</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>15</v>
+      </c>
+      <c r="B100" t="s">
+        <v>16</v>
+      </c>
+      <c r="C100" t="n">
+        <v>-1.07769265196076</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>15</v>
+      </c>
+      <c r="B101" t="s">
+        <v>16</v>
+      </c>
+      <c r="C101" t="n">
+        <v>-1.07957241163961</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>15</v>
+      </c>
+      <c r="B102" t="s">
+        <v>16</v>
+      </c>
+      <c r="C102" t="n">
+        <v>0.0219368398346981</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>15</v>
+      </c>
+      <c r="B103" t="s">
+        <v>16</v>
+      </c>
+      <c r="C103" t="n">
+        <v>-0.510512327721214</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>15</v>
+      </c>
+      <c r="B104" t="s">
+        <v>16</v>
+      </c>
+      <c r="C104" t="n">
+        <v>-0.224822200455143</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>15</v>
+      </c>
+      <c r="B105" t="s">
+        <v>16</v>
+      </c>
+      <c r="C105" t="n">
+        <v>-0.559373937272448</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>15</v>
+      </c>
+      <c r="B106" t="s">
+        <v>16</v>
+      </c>
+      <c r="C106" t="n">
+        <v>-0.502504358767361</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>15</v>
+      </c>
+      <c r="B107" t="s">
+        <v>16</v>
+      </c>
+      <c r="C107" t="n">
+        <v>-0.850653991447038</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>15</v>
+      </c>
+      <c r="B108" t="s">
+        <v>16</v>
+      </c>
+      <c r="C108" t="n">
+        <v>-0.130209011699243</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>15</v>
+      </c>
+      <c r="B109" t="s">
+        <v>16</v>
+      </c>
+      <c r="C109" t="n">
+        <v>-0.356027368410637</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>15</v>
+      </c>
+      <c r="B110" t="s">
+        <v>16</v>
+      </c>
+      <c r="C110" t="n">
+        <v>-0.220925567442153</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>15</v>
+      </c>
+      <c r="B111" t="s">
+        <v>16</v>
+      </c>
+      <c r="C111" t="n">
+        <v>-3.07230974034111</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>15</v>
+      </c>
+      <c r="B112" t="s">
+        <v>16</v>
+      </c>
+      <c r="C112" t="n">
+        <v>-1.05082974072912</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>15</v>
+      </c>
+      <c r="B113" t="s">
+        <v>16</v>
+      </c>
+      <c r="C113" t="n">
+        <v>-1.33668631149169</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>15</v>
+      </c>
+      <c r="B114" t="s">
+        <v>16</v>
+      </c>
+      <c r="C114" t="n">
+        <v>-0.73986645574744</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>15</v>
+      </c>
+      <c r="B115" t="s">
+        <v>16</v>
+      </c>
+      <c r="C115" t="n">
+        <v>-1.31980083905773</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>15</v>
+      </c>
+      <c r="B116" t="s">
+        <v>16</v>
+      </c>
+      <c r="C116" t="n">
+        <v>-0.817888354130003</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>15</v>
+      </c>
+      <c r="B117" t="s">
+        <v>16</v>
+      </c>
+      <c r="C117" t="n">
+        <v>-0.93896917402071</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>15</v>
+      </c>
+      <c r="B118" t="s">
+        <v>16</v>
+      </c>
+      <c r="C118" t="n">
+        <v>-0.580384471896491</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>15</v>
+      </c>
+      <c r="B119" t="s">
+        <v>16</v>
+      </c>
+      <c r="C119" t="n">
+        <v>-0.59593393007914</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>15</v>
+      </c>
+      <c r="B120" t="s">
+        <v>16</v>
+      </c>
+      <c r="C120" t="n">
+        <v>-0.782009046450609</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>15</v>
+      </c>
+      <c r="B121" t="s">
+        <v>16</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.347165425308255</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>15</v>
+      </c>
+      <c r="B122" t="s">
+        <v>16</v>
+      </c>
+      <c r="C122" t="n">
+        <v>-0.719535623074161</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>15</v>
+      </c>
+      <c r="B123" t="s">
+        <v>16</v>
+      </c>
+      <c r="C123" t="n">
+        <v>-1.10740694640731</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>15</v>
+      </c>
+      <c r="B124" t="s">
+        <v>16</v>
+      </c>
+      <c r="C124" t="n">
+        <v>-0.63086142875298</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>15</v>
+      </c>
+      <c r="B125" t="s">
+        <v>16</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.466827141520165</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>15</v>
+      </c>
+      <c r="B126" t="s">
+        <v>16</v>
+      </c>
+      <c r="C126" t="n">
+        <v>-1.05940689381613</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>15</v>
+      </c>
+      <c r="B127" t="s">
+        <v>16</v>
+      </c>
+      <c r="C127" t="n">
+        <v>-1.71706066787428</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>15</v>
+      </c>
+      <c r="B128" t="s">
+        <v>16</v>
+      </c>
+      <c r="C128" t="n">
+        <v>-0.203905467876975</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>15</v>
+      </c>
+      <c r="B129" t="s">
+        <v>16</v>
+      </c>
+      <c r="C129" t="n">
+        <v>-0.111442590457397</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>15</v>
+      </c>
+      <c r="B130" t="s">
+        <v>16</v>
+      </c>
+      <c r="C130" t="n">
+        <v>-0.303177534814485</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>15</v>
+      </c>
+      <c r="B131" t="s">
+        <v>16</v>
+      </c>
+      <c r="C131" t="n">
+        <v>-0.636570916613976</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>15</v>
+      </c>
+      <c r="B132" t="s">
+        <v>16</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.106505926004901</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>15</v>
+      </c>
+      <c r="B133" t="s">
+        <v>16</v>
+      </c>
+      <c r="C133" t="n">
+        <v>-0.642197419956146</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>15</v>
+      </c>
+      <c r="B134" t="s">
+        <v>16</v>
+      </c>
+      <c r="C134" t="n">
+        <v>-0.147145379455883</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>15</v>
+      </c>
+      <c r="B135" t="s">
+        <v>16</v>
+      </c>
+      <c r="C135" t="n">
+        <v>-0.248423871543631</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>15</v>
+      </c>
+      <c r="B136" t="s">
+        <v>16</v>
+      </c>
+      <c r="C136" t="n">
+        <v>-0.238100449619287</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>15</v>
+      </c>
+      <c r="B137" t="s">
+        <v>16</v>
+      </c>
+      <c r="C137" t="n">
+        <v>-0.488414986026892</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>15</v>
+      </c>
+      <c r="B138" t="s">
+        <v>16</v>
+      </c>
+      <c r="C138" t="n">
+        <v>-0.273925929436164</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>15</v>
+      </c>
+      <c r="B139" t="s">
+        <v>16</v>
+      </c>
+      <c r="C139" t="n">
+        <v>-0.47814042497357</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>15</v>
+      </c>
+      <c r="B140" t="s">
+        <v>16</v>
+      </c>
+      <c r="C140" t="n">
+        <v>-0.766006478654984</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>15</v>
+      </c>
+      <c r="B141" t="s">
+        <v>16</v>
+      </c>
+      <c r="C141" t="n">
+        <v>-0.978660397373685</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>15</v>
+      </c>
+      <c r="B142" t="s">
+        <v>16</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.0476534870606725</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>15</v>
+      </c>
+      <c r="B143" t="s">
+        <v>16</v>
+      </c>
+      <c r="C143" t="n">
+        <v>-0.233184393945031</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>15</v>
+      </c>
+      <c r="B144" t="s">
+        <v>16</v>
+      </c>
+      <c r="C144" t="n">
+        <v>-1.317705326937</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>15</v>
+      </c>
+      <c r="B145" t="s">
+        <v>16</v>
+      </c>
+      <c r="C145" t="n">
+        <v>0.135899031147733</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>15</v>
+      </c>
+      <c r="B146" t="s">
+        <v>16</v>
+      </c>
+      <c r="C146" t="n">
+        <v>-0.343237563922429</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>15</v>
+      </c>
+      <c r="B147" t="s">
+        <v>16</v>
+      </c>
+      <c r="C147" t="n">
+        <v>-0.520927580260777</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>15</v>
+      </c>
+      <c r="B148" t="s">
+        <v>16</v>
+      </c>
+      <c r="C148" t="n">
+        <v>-0.166741488993661</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>15</v>
+      </c>
+      <c r="B149" t="s">
+        <v>16</v>
+      </c>
+      <c r="C149" t="n">
+        <v>0.382367901986676</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>15</v>
+      </c>
+      <c r="B150" t="s">
+        <v>16</v>
+      </c>
+      <c r="C150" t="n">
+        <v>-0.156783719765036</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>15</v>
+      </c>
+      <c r="B151" t="s">
+        <v>16</v>
+      </c>
+      <c r="C151" t="n">
+        <v>-0.473782415195085</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" t="s">
+        <v>16</v>
+      </c>
+      <c r="C152" t="n">
+        <v>-1.15522725231708</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>15</v>
+      </c>
+      <c r="B153" t="s">
+        <v>16</v>
+      </c>
+      <c r="C153" t="n">
+        <v>-1.76798603971624</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>15</v>
+      </c>
+      <c r="B154" t="s">
+        <v>16</v>
+      </c>
+      <c r="C154" t="n">
+        <v>-0.281260140036155</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>15</v>
+      </c>
+      <c r="B155" t="s">
+        <v>16</v>
+      </c>
+      <c r="C155" t="n">
+        <v>-0.92862395800032</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>15</v>
+      </c>
+      <c r="B156" t="s">
+        <v>16</v>
+      </c>
+      <c r="C156" t="n">
+        <v>-0.265134951331497</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>15</v>
+      </c>
+      <c r="B157" t="s">
+        <v>16</v>
+      </c>
+      <c r="C157" t="n">
+        <v>-0.298548983689381</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>15</v>
+      </c>
+      <c r="B158" t="s">
+        <v>16</v>
+      </c>
+      <c r="C158" t="n">
+        <v>-0.916993408327079</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>15</v>
+      </c>
+      <c r="B159" t="s">
+        <v>16</v>
+      </c>
+      <c r="C159" t="n">
+        <v>-0.209487087425797</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>15</v>
+      </c>
+      <c r="B160" t="s">
+        <v>16</v>
+      </c>
+      <c r="C160" t="n">
+        <v>-0.37580500977307</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>15</v>
+      </c>
+      <c r="B161" t="s">
+        <v>16</v>
+      </c>
+      <c r="C161" t="n">
+        <v>-0.5971713420797</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>15</v>
+      </c>
+      <c r="B162" t="s">
+        <v>16</v>
+      </c>
+      <c r="C162" t="n">
+        <v>0.0842265810635363</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>15</v>
+      </c>
+      <c r="B163" t="s">
+        <v>16</v>
+      </c>
+      <c r="C163" t="n">
+        <v>-0.698162976333456</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>15</v>
+      </c>
+      <c r="B164" t="s">
+        <v>16</v>
+      </c>
+      <c r="C164" t="n">
+        <v>0.00960022113025472</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>15</v>
+      </c>
+      <c r="B165" t="s">
+        <v>16</v>
+      </c>
+      <c r="C165" t="n">
+        <v>-0.296905556803003</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>15</v>
+      </c>
+      <c r="B166" t="s">
+        <v>16</v>
+      </c>
+      <c r="C166" t="n">
+        <v>-1.44661203487034</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>15</v>
+      </c>
+      <c r="B167" t="s">
+        <v>16</v>
+      </c>
+      <c r="C167" t="n">
+        <v>-2.14400328380652</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>15</v>
+      </c>
+      <c r="B168" t="s">
+        <v>16</v>
+      </c>
+      <c r="C168" t="n">
+        <v>-1.03140436415662</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>15</v>
+      </c>
+      <c r="B169" t="s">
+        <v>16</v>
+      </c>
+      <c r="C169" t="n">
+        <v>-0.0876391276039843</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>15</v>
+      </c>
+      <c r="B170" t="s">
+        <v>16</v>
+      </c>
+      <c r="C170" t="n">
+        <v>-0.356895859108949</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>15</v>
+      </c>
+      <c r="B171" t="s">
+        <v>16</v>
+      </c>
+      <c r="C171" t="n">
+        <v>-0.0181312388581691</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>15</v>
+      </c>
+      <c r="B172" t="s">
+        <v>16</v>
+      </c>
+      <c r="C172" t="n">
+        <v>-0.119365293667963</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>15</v>
+      </c>
+      <c r="B173" t="s">
+        <v>16</v>
+      </c>
+      <c r="C173" t="n">
+        <v>-1.04215200519873</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>15</v>
+      </c>
+      <c r="B174" t="s">
+        <v>16</v>
+      </c>
+      <c r="C174" t="n">
+        <v>-0.535062432095253</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>15</v>
+      </c>
+      <c r="B175" t="s">
+        <v>16</v>
+      </c>
+      <c r="C175" t="n">
+        <v>-0.190058807480494</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>15</v>
+      </c>
+      <c r="B176" t="s">
+        <v>16</v>
+      </c>
+      <c r="C176" t="n">
+        <v>-0.785807117639157</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>15</v>
+      </c>
+      <c r="B177" t="s">
+        <v>16</v>
+      </c>
+      <c r="C177" t="n">
+        <v>-0.209164195912003</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>15</v>
+      </c>
+      <c r="B178" t="s">
+        <v>16</v>
+      </c>
+      <c r="C178" t="n">
+        <v>-0.988223219663783</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>15</v>
+      </c>
+      <c r="B179" t="s">
+        <v>16</v>
+      </c>
+      <c r="C179" t="n">
+        <v>-0.182433737403852</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>15</v>
+      </c>
+      <c r="B180" t="s">
+        <v>16</v>
+      </c>
+      <c r="C180" t="n">
+        <v>-0.138170670974138</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>15</v>
+      </c>
+      <c r="B181" t="s">
+        <v>16</v>
+      </c>
+      <c r="C181" t="n">
+        <v>0.61853585398373</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>15</v>
+      </c>
+      <c r="B182" t="s">
+        <v>16</v>
+      </c>
+      <c r="C182" t="n">
+        <v>0.161340991479431</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>15</v>
+      </c>
+      <c r="B183" t="s">
+        <v>16</v>
+      </c>
+      <c r="C183" t="n">
+        <v>-1.73810857171988</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>15</v>
+      </c>
+      <c r="B184" t="s">
+        <v>16</v>
+      </c>
+      <c r="C184" t="n">
+        <v>-0.211590812763894</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>15</v>
+      </c>
+      <c r="B185" t="s">
+        <v>16</v>
+      </c>
+      <c r="C185" t="n">
+        <v>-1.12937224199908</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>15</v>
+      </c>
+      <c r="B186" t="s">
+        <v>16</v>
+      </c>
+      <c r="C186" t="n">
+        <v>-1.4392638346944</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>15</v>
+      </c>
+      <c r="B187" t="s">
+        <v>16</v>
+      </c>
+      <c r="C187" t="n">
+        <v>-0.953884021577716</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>15</v>
+      </c>
+      <c r="B188" t="s">
+        <v>16</v>
+      </c>
+      <c r="C188" t="n">
+        <v>-1.18798903422317</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>15</v>
+      </c>
+      <c r="B189" t="s">
+        <v>16</v>
+      </c>
+      <c r="C189" t="n">
+        <v>-0.432391088988596</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>15</v>
+      </c>
+      <c r="B190" t="s">
+        <v>16</v>
+      </c>
+      <c r="C190" t="n">
+        <v>-0.577209012807019</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>15</v>
+      </c>
+      <c r="B191" t="s">
+        <v>16</v>
+      </c>
+      <c r="C191" t="n">
+        <v>-0.700216639818878</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>15</v>
+      </c>
+      <c r="B192" t="s">
+        <v>16</v>
+      </c>
+      <c r="C192" t="n">
+        <v>-1.31772049525437</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>15</v>
+      </c>
+      <c r="B193" t="s">
+        <v>16</v>
+      </c>
+      <c r="C193" t="n">
+        <v>-0.857442081320422</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>15</v>
+      </c>
+      <c r="B194" t="s">
+        <v>16</v>
+      </c>
+      <c r="C194" t="n">
+        <v>-0.957764527306677</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>15</v>
+      </c>
+      <c r="B195" t="s">
+        <v>16</v>
+      </c>
+      <c r="C195" t="n">
+        <v>-0.741455993229308</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>15</v>
+      </c>
+      <c r="B196" t="s">
+        <v>16</v>
+      </c>
+      <c r="C196" t="n">
+        <v>-0.492325831080101</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>15</v>
+      </c>
+      <c r="B197" t="s">
+        <v>16</v>
+      </c>
+      <c r="C197" t="n">
+        <v>-0.379719763641928</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>15</v>
+      </c>
+      <c r="B198" t="s">
+        <v>16</v>
+      </c>
+      <c r="C198" t="n">
+        <v>-0.655514748481907</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>15</v>
+      </c>
+      <c r="B199" t="s">
+        <v>16</v>
+      </c>
+      <c r="C199" t="n">
+        <v>-1.21380296681095</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>15</v>
+      </c>
+      <c r="B200" t="s">
+        <v>16</v>
+      </c>
+      <c r="C200" t="n">
+        <v>-0.402280937177602</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>15</v>
+      </c>
+      <c r="B201" t="s">
+        <v>16</v>
+      </c>
+      <c r="C201" t="n">
+        <v>-0.347783388681987</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
